--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="155">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -453,6 +453,9 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
+  </si>
+  <si>
+    <t>AssociatedEntity.sdtcSpecialty</t>
   </si>
   <si>
     <t>AssociatedEntity.addr</t>
@@ -794,7 +797,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.34765625" customWidth="true" bestFit="true"/>
@@ -2911,11 +2914,9 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2986,10 +2987,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3012,10 +3013,10 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -3067,7 +3068,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3087,10 +3088,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3101,7 +3102,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>
@@ -3113,10 +3114,10 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -3168,13 +3169,13 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>74</v>
@@ -3188,10 +3189,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3214,10 +3215,10 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -3269,7 +3270,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3284,6 +3285,107 @@
         <v>74</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK25" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
